--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -441,10 +441,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>448.4</v>
+        <v>409.5</v>
       </c>
       <c r="C2" t="n">
-        <v>451.6</v>
+        <v>403.85</v>
       </c>
     </row>
     <row r="3">
@@ -454,10 +454,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7569.75</v>
+        <v>6959.2</v>
       </c>
       <c r="C3" t="n">
-        <v>7552.4</v>
+        <v>6921.25</v>
       </c>
     </row>
     <row r="4">
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2495.85</v>
+        <v>2338.95</v>
       </c>
       <c r="C4" t="n">
-        <v>2506.4</v>
+        <v>2344.95</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>549.1</v>
+        <v>532.1</v>
       </c>
       <c r="C5" t="n">
-        <v>541.8</v>
+        <v>531.95</v>
       </c>
     </row>
     <row r="6">
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>228.66</v>
+        <v>218.94</v>
       </c>
       <c r="C6" t="n">
-        <v>232.18</v>
+        <v>217.28</v>
       </c>
     </row>
     <row r="7">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1637.05</v>
+        <v>1563.4</v>
       </c>
       <c r="C7" t="n">
-        <v>1635.2</v>
+        <v>1569.65</v>
       </c>
     </row>
     <row r="8">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6868.35</v>
+        <v>6866.7</v>
       </c>
       <c r="C8" t="n">
-        <v>6850.3</v>
+        <v>6848.25</v>
       </c>
     </row>
     <row r="9">
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174.55</v>
+        <v>164.38</v>
       </c>
       <c r="C9" t="n">
-        <v>176.27</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="10">
@@ -545,10 +545,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>249.55</v>
+        <v>240.95</v>
       </c>
       <c r="C10" t="n">
-        <v>249.05</v>
+        <v>235.3</v>
       </c>
     </row>
     <row r="11">
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>262.93</v>
+        <v>246.25</v>
       </c>
       <c r="C11" t="n">
-        <v>264.6</v>
+        <v>240.59</v>
       </c>
     </row>
     <row r="12">
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53531</v>
+        <v>51303.15</v>
       </c>
       <c r="C12" t="n">
-        <v>53717.85</v>
+        <v>50769.95</v>
       </c>
     </row>
     <row r="13">
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>528.15</v>
+        <v>507.75</v>
       </c>
       <c r="C13" t="n">
-        <v>542.65</v>
+        <v>509.15</v>
       </c>
     </row>
     <row r="14">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17345.9</v>
+        <v>17998.45</v>
       </c>
       <c r="C14" t="n">
-        <v>17421.05</v>
+        <v>17944.9</v>
       </c>
     </row>
     <row r="15">
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>862.7</v>
+        <v>844.25</v>
       </c>
       <c r="C15" t="n">
-        <v>856.85</v>
+        <v>830.7</v>
       </c>
     </row>
     <row r="16">
@@ -623,10 +623,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4842.1</v>
+        <v>4750.55</v>
       </c>
       <c r="C16" t="n">
-        <v>4877.05</v>
+        <v>4734.5</v>
       </c>
     </row>
     <row r="17">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3546.4</v>
+        <v>3143.6</v>
       </c>
       <c r="C17" t="n">
-        <v>3524.8</v>
+        <v>3162.05</v>
       </c>
     </row>
     <row r="18">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>213.77</v>
+        <v>197.02</v>
       </c>
       <c r="C18" t="n">
-        <v>213.4</v>
+        <v>194.46</v>
       </c>
     </row>
     <row r="19">
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1909.9</v>
+        <v>1903</v>
       </c>
       <c r="C19" t="n">
-        <v>1922.7</v>
+        <v>1911.35</v>
       </c>
     </row>
     <row r="20">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>670.9</v>
+        <v>634.15</v>
       </c>
       <c r="C20" t="n">
-        <v>670.15</v>
+        <v>622.65</v>
       </c>
     </row>
     <row r="21">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>385.55</v>
+        <v>390.1</v>
       </c>
       <c r="C21" t="n">
-        <v>384</v>
+        <v>388.3</v>
       </c>
     </row>
     <row r="22">
@@ -701,10 +701,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>982.6</v>
+        <v>945.7</v>
       </c>
       <c r="C22" t="n">
-        <v>990.35</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="23">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>967.2</v>
+        <v>940.8</v>
       </c>
       <c r="C23" t="n">
-        <v>949.1</v>
+        <v>908.05</v>
       </c>
     </row>
     <row r="24">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>630.15</v>
+        <v>583.25</v>
       </c>
       <c r="C24" t="n">
-        <v>641.25</v>
+        <v>582.25</v>
       </c>
     </row>
     <row r="25">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3051.25</v>
+        <v>2909.3</v>
       </c>
       <c r="C25" t="n">
-        <v>3073</v>
+        <v>2906.35</v>
       </c>
     </row>
     <row r="26">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>279.15</v>
+        <v>265.15</v>
       </c>
       <c r="C26" t="n">
-        <v>278</v>
+        <v>266.05</v>
       </c>
     </row>
     <row r="27">
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24694.6</v>
+        <v>23769.75</v>
       </c>
       <c r="C27" t="n">
-        <v>24783.25</v>
+        <v>23625.65</v>
       </c>
     </row>
     <row r="28">
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>369.85</v>
+        <v>333.65</v>
       </c>
       <c r="C28" t="n">
-        <v>369.5</v>
+        <v>333.25</v>
       </c>
     </row>
     <row r="29">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>258.9</v>
+        <v>240.85</v>
       </c>
       <c r="C29" t="n">
-        <v>260.05</v>
+        <v>237.1</v>
       </c>
     </row>
     <row r="30">
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>563.7</v>
+        <v>512.4</v>
       </c>
       <c r="C30" t="n">
-        <v>559.1</v>
+        <v>513.25</v>
       </c>
     </row>
     <row r="31">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1295.15</v>
+        <v>1222.3</v>
       </c>
       <c r="C31" t="n">
-        <v>1311.55</v>
+        <v>1205.3</v>
       </c>
     </row>
     <row r="32">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>858.05</v>
+        <v>821.15</v>
       </c>
       <c r="C32" t="n">
-        <v>863.65</v>
+        <v>812</v>
       </c>
     </row>
     <row r="33">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>754.95</v>
+        <v>706.1</v>
       </c>
       <c r="C33" t="n">
-        <v>765.85</v>
+        <v>696.85</v>
       </c>
     </row>
     <row r="34">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>798.75</v>
+        <v>722.2</v>
       </c>
       <c r="C34" t="n">
-        <v>816.8</v>
+        <v>724.05</v>
       </c>
     </row>
     <row r="35">
@@ -870,10 +870,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>440.75</v>
+        <v>399.9</v>
       </c>
       <c r="C35" t="n">
-        <v>439.7</v>
+        <v>401.1</v>
       </c>
     </row>
     <row r="36">
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>149.88</v>
+        <v>141.71</v>
       </c>
       <c r="C36" t="n">
-        <v>148.29</v>
+        <v>140.68</v>
       </c>
     </row>
     <row r="37">
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1958.35</v>
+        <v>1999.35</v>
       </c>
       <c r="C37" t="n">
-        <v>1968.55</v>
+        <v>2025.35</v>
       </c>
     </row>
   </sheetData>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>721.9</v>
+        <v>403.85</v>
       </c>
       <c r="C2" t="n">
-        <v>718.45</v>
+        <v>403.85</v>
       </c>
     </row>
     <row r="3">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>3147.9</v>
+        <v>6959.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3144.25</v>
+        <v>6921.25</v>
       </c>
     </row>
     <row r="4">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>524.35</v>
+        <v>2344.95</v>
       </c>
       <c r="C4" t="n">
-        <v>528.5</v>
+        <v>2344.95</v>
       </c>
     </row>
     <row r="5">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1579.6</v>
+        <v>531.95</v>
       </c>
       <c r="C5" t="n">
-        <v>1585.7</v>
+        <v>531.95</v>
       </c>
     </row>
     <row r="6">
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>7138</v>
+        <v>218.94</v>
       </c>
       <c r="C6" t="n">
-        <v>7107.05</v>
+        <v>217.28</v>
       </c>
     </row>
     <row r="7">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204.33</v>
+        <v>1569.65</v>
       </c>
       <c r="C7" t="n">
-        <v>208.06</v>
+        <v>1569.65</v>
       </c>
     </row>
     <row r="8">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>273.8</v>
+        <v>6848.25</v>
       </c>
       <c r="C8" t="n">
-        <v>270.15</v>
+        <v>6848.25</v>
       </c>
     </row>
     <row r="9">
@@ -1027,10 +1027,10 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>52724.1</v>
+        <v>159.05</v>
       </c>
       <c r="C9" t="n">
-        <v>53166.2</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="10">
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>832.8</v>
+        <v>240.95</v>
       </c>
       <c r="C10" t="n">
-        <v>838.6</v>
+        <v>235.3</v>
       </c>
     </row>
     <row r="11">
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>4737.3</v>
+        <v>240.59</v>
       </c>
       <c r="C11" t="n">
-        <v>4689.5</v>
+        <v>240.59</v>
       </c>
     </row>
     <row r="12">
@@ -1066,7 +1066,10 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>4130.75</v>
+        <v>51303.15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>50769.95</v>
       </c>
     </row>
     <row r="13">
@@ -1076,10 +1079,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>186.19</v>
+        <v>507.75</v>
       </c>
       <c r="C13" t="n">
-        <v>180.97</v>
+        <v>509.15</v>
       </c>
     </row>
     <row r="14">
@@ -1089,10 +1092,10 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>1519.4</v>
+        <v>17998.45</v>
       </c>
       <c r="C14" t="n">
-        <v>1522.35</v>
+        <v>17944.9</v>
       </c>
     </row>
     <row r="15">
@@ -1102,10 +1105,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>699.15</v>
+        <v>830.7</v>
       </c>
       <c r="C15" t="n">
-        <v>691.85</v>
+        <v>830.7</v>
       </c>
     </row>
     <row r="16">
@@ -1115,7 +1118,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>522.3</v>
+        <v>4734.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4734.5</v>
       </c>
     </row>
     <row r="17">
@@ -1125,10 +1131,10 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>1434.25</v>
+        <v>3143.6</v>
       </c>
       <c r="C17" t="n">
-        <v>1442.85</v>
+        <v>3162.05</v>
       </c>
     </row>
     <row r="18">
@@ -1138,10 +1144,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1050.5</v>
+        <v>194.46</v>
       </c>
       <c r="C18" t="n">
-        <v>1055.45</v>
+        <v>194.46</v>
       </c>
     </row>
     <row r="19">
@@ -1151,10 +1157,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>795.7</v>
+        <v>1911.35</v>
       </c>
       <c r="C19" t="n">
-        <v>793</v>
+        <v>1911.35</v>
       </c>
     </row>
     <row r="20">
@@ -1164,10 +1170,10 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>2880.6</v>
+        <v>622.65</v>
       </c>
       <c r="C20" t="n">
-        <v>2902.8</v>
+        <v>622.65</v>
       </c>
     </row>
     <row r="21">
@@ -1177,10 +1183,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>300.5</v>
+        <v>390.1</v>
       </c>
       <c r="C21" t="n">
-        <v>298.2</v>
+        <v>388.3</v>
       </c>
     </row>
     <row r="22">
@@ -1190,10 +1196,10 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>24379.4</v>
+        <v>929.45</v>
       </c>
       <c r="C22" t="n">
-        <v>24359.45</v>
+        <v>929.45</v>
       </c>
     </row>
     <row r="23">
@@ -1203,10 +1209,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>379.8</v>
+        <v>908.05</v>
       </c>
       <c r="C23" t="n">
-        <v>372.95</v>
+        <v>908.05</v>
       </c>
     </row>
     <row r="24">
@@ -1216,10 +1222,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>859.75</v>
+        <v>582.25</v>
       </c>
       <c r="C24" t="n">
-        <v>839.3</v>
+        <v>582.25</v>
       </c>
     </row>
     <row r="25">
@@ -1229,10 +1235,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>784.55</v>
+        <v>2906.35</v>
       </c>
       <c r="C25" t="n">
-        <v>781.05</v>
+        <v>2906.35</v>
       </c>
     </row>
     <row r="26">
@@ -1242,10 +1248,10 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>993.65</v>
+        <v>266.05</v>
       </c>
       <c r="C26" t="n">
-        <v>998.2</v>
+        <v>266.05</v>
       </c>
     </row>
     <row r="27">
@@ -1255,10 +1261,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>439.95</v>
+        <v>23769.75</v>
       </c>
       <c r="C27" t="n">
-        <v>436.25</v>
+        <v>23625.65</v>
       </c>
     </row>
     <row r="28">
@@ -1268,10 +1274,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.71</v>
+        <v>333.25</v>
       </c>
       <c r="C28" t="n">
-        <v>176.29</v>
+        <v>333.25</v>
       </c>
     </row>
     <row r="29">
@@ -1281,7 +1287,74 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>473.85</v>
+        <v>240.85</v>
+      </c>
+      <c r="C29" t="n">
+        <v>237.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>512.4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>513.25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1205.3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1205.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>812</v>
+      </c>
+      <c r="C32" t="n">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>696.85</v>
+      </c>
+      <c r="C33" t="n">
+        <v>696.85</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>724.05</v>
+      </c>
+      <c r="C34" t="n">
+        <v>724.05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>401.1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>140.68</v>
+      </c>
+      <c r="C36" t="n">
+        <v>140.68</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1999.35</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2025.35</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -10,13 +10,15 @@
     <sheet name="Sheet3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,9 +48,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -440,11 +444,11 @@
           <t>AARTIIND</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>409.5</v>
+      <c r="B2" s="3" t="n">
+        <v>439.4</v>
       </c>
       <c r="C2" t="n">
-        <v>403.85</v>
+        <v>429.75</v>
       </c>
     </row>
     <row r="3">
@@ -453,11 +457,11 @@
           <t>ABB</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>6959.2</v>
+      <c r="B3" s="3" t="n">
+        <v>6318</v>
       </c>
       <c r="C3" t="n">
-        <v>6921.25</v>
+        <v>6193.75</v>
       </c>
     </row>
     <row r="4">
@@ -466,11 +470,11 @@
           <t>ADANI</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>2338.95</v>
+      <c r="B4" s="3" t="n">
+        <v>2433</v>
       </c>
       <c r="C4" t="n">
-        <v>2344.95</v>
+        <v>2388.15</v>
       </c>
     </row>
     <row r="5">
@@ -479,11 +483,11 @@
           <t>APOLLO</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>532.1</v>
+      <c r="B5" s="3" t="n">
+        <v>455.6</v>
       </c>
       <c r="C5" t="n">
-        <v>531.95</v>
+        <v>454.75</v>
       </c>
     </row>
     <row r="6">
@@ -492,11 +496,11 @@
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>218.94</v>
+      <c r="B6" s="3" t="n">
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>217.28</v>
+        <v>206.68</v>
       </c>
     </row>
     <row r="7">
@@ -505,11 +509,11 @@
           <t>BAJFINSV</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1563.4</v>
+      <c r="B7" s="3" t="n">
+        <v>1695.9</v>
       </c>
       <c r="C7" t="n">
-        <v>1569.65</v>
+        <v>1671.65</v>
       </c>
     </row>
     <row r="8">
@@ -518,11 +522,11 @@
           <t>BAJFIN</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>6866.7</v>
+      <c r="B8" s="3" t="n">
+        <v>7253.05</v>
       </c>
       <c r="C8" t="n">
-        <v>6848.25</v>
+        <v>7177.4</v>
       </c>
     </row>
     <row r="9">
@@ -531,11 +535,11 @@
           <t>BANBK</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>164.38</v>
+      <c r="B9" s="3" t="n">
+        <v>151.5</v>
       </c>
       <c r="C9" t="n">
-        <v>159.05</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="10">
@@ -544,11 +548,11 @@
           <t>BHEL</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>240.95</v>
+      <c r="B10" s="3" t="n">
+        <v>210.59</v>
       </c>
       <c r="C10" t="n">
-        <v>235.3</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="11">
@@ -557,11 +561,11 @@
           <t>BARODA</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>246.25</v>
+      <c r="B11" s="3" t="n">
+        <v>229.05</v>
       </c>
       <c r="C11" t="n">
-        <v>240.59</v>
+        <v>222.02</v>
       </c>
     </row>
     <row r="12">
@@ -570,11 +574,11 @@
           <t>BN</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>51303.15</v>
+      <c r="B12" s="3" t="n">
+        <v>49443.95</v>
       </c>
       <c r="C12" t="n">
-        <v>50769.95</v>
+        <v>48892.55</v>
       </c>
     </row>
     <row r="13">
@@ -583,323 +587,336 @@
           <t>CHAMBAL</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>507.75</v>
+      <c r="B13" s="3" t="n">
+        <v>497</v>
       </c>
       <c r="C13" t="n">
-        <v>509.15</v>
+        <v>485.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>17998.45</v>
+          <t>COALIND</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>381</v>
       </c>
       <c r="C14" t="n">
-        <v>17944.9</v>
+        <v>374.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>844.25</v>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>16944.45</v>
       </c>
       <c r="C15" t="n">
-        <v>830.7</v>
+        <v>16919.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EICHER</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>4750.55</v>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>742</v>
       </c>
       <c r="C16" t="n">
-        <v>4734.5</v>
+        <v>734.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESCORTS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3143.6</v>
+          <t>EICHER</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5060.95</v>
       </c>
       <c r="C17" t="n">
-        <v>3162.05</v>
+        <v>5081.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FEDBANK</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>197.02</v>
+          <t>ESCORTS</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>3564</v>
       </c>
       <c r="C18" t="n">
-        <v>194.46</v>
+        <v>3478.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HCL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1903</v>
+          <t>FEDBANK</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>195.8</v>
       </c>
       <c r="C19" t="n">
-        <v>1911.35</v>
+        <v>194.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>634.15</v>
+          <t>HCL</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1792.25</v>
       </c>
       <c r="C20" t="n">
-        <v>622.65</v>
+        <v>1825.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IGL</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>390.1</v>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>602.5</v>
       </c>
       <c r="C21" t="n">
-        <v>388.3</v>
+        <v>591.55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INDUSIND</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>945.7</v>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>397.45</v>
       </c>
       <c r="C22" t="n">
-        <v>929.45</v>
+        <v>402.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JIND</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>940.8</v>
+          <t>INDUSIND</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>975.35</v>
       </c>
       <c r="C23" t="n">
-        <v>908.05</v>
+        <v>962.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LIC</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>583.25</v>
+          <t>JIND</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>917</v>
       </c>
       <c r="C24" t="n">
-        <v>582.25</v>
+        <v>910.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2909.3</v>
+          <t>LIC</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>565.3</v>
       </c>
       <c r="C25" t="n">
-        <v>2906.35</v>
+        <v>552.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>265.15</v>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2979.75</v>
       </c>
       <c r="C26" t="n">
-        <v>266.05</v>
+        <v>2960.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>23769.75</v>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>269.85</v>
       </c>
       <c r="C27" t="n">
-        <v>23625.65</v>
+        <v>267.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>333.65</v>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>23377.55</v>
       </c>
       <c r="C28" t="n">
-        <v>333.25</v>
+        <v>23265.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>240.85</v>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>327</v>
       </c>
       <c r="C29" t="n">
-        <v>237.1</v>
+        <v>321.35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RECLTD</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>512.4</v>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>263.35</v>
       </c>
       <c r="C30" t="n">
-        <v>513.25</v>
+        <v>258.18</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>REL</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1222.3</v>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>485.4</v>
       </c>
       <c r="C31" t="n">
-        <v>1205.3</v>
+        <v>478.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>821.15</v>
+          <t>REL</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1275</v>
       </c>
       <c r="C32" t="n">
-        <v>812</v>
+        <v>1252.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>706.1</v>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>767</v>
       </c>
       <c r="C33" t="n">
-        <v>696.85</v>
+        <v>753.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TM</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>722.2</v>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>652.9</v>
       </c>
       <c r="C34" t="n">
-        <v>724.05</v>
+        <v>653.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>399.9</v>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>775.45</v>
       </c>
       <c r="C35" t="n">
-        <v>401.1</v>
+        <v>763.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>141.71</v>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>369</v>
       </c>
       <c r="C36" t="n">
-        <v>140.68</v>
+        <v>365.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>127.81</v>
+      </c>
+      <c r="C37" t="n">
+        <v>126.53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>VEDL</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1999.35</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2025.35</v>
+      <c r="B38" t="n">
+        <v>450.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>435.25</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet3" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -48,10 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -444,11 +443,11 @@
           <t>AARTIIND</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>439.4</v>
+      <c r="B2" s="2" t="n">
+        <v>444.7</v>
       </c>
       <c r="C2" t="n">
-        <v>429.75</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3">
@@ -457,11 +456,11 @@
           <t>ABB</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>6318</v>
+      <c r="B3" s="2" t="n">
+        <v>5874.65</v>
       </c>
       <c r="C3" t="n">
-        <v>6193.75</v>
+        <v>5719.35</v>
       </c>
     </row>
     <row r="4">
@@ -470,11 +469,11 @@
           <t>ADANI</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>2433</v>
+      <c r="B4" s="2" t="n">
+        <v>2287.8</v>
       </c>
       <c r="C4" t="n">
-        <v>2388.15</v>
+        <v>2252.6</v>
       </c>
     </row>
     <row r="5">
@@ -483,11 +482,11 @@
           <t>APOLLO</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>455.6</v>
+      <c r="B5" s="2" t="n">
+        <v>437.3</v>
       </c>
       <c r="C5" t="n">
-        <v>454.75</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="6">
@@ -496,11 +495,11 @@
           <t>ASHOKLEY</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>208</v>
+      <c r="B6" s="2" t="n">
+        <v>216.83</v>
       </c>
       <c r="C6" t="n">
-        <v>206.68</v>
+        <v>210.33</v>
       </c>
     </row>
     <row r="7">
@@ -509,11 +508,11 @@
           <t>BAJFINSV</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>1695.9</v>
+      <c r="B7" s="2" t="n">
+        <v>1736.1</v>
       </c>
       <c r="C7" t="n">
-        <v>1671.65</v>
+        <v>1745.2</v>
       </c>
     </row>
     <row r="8">
@@ -522,11 +521,11 @@
           <t>BAJFIN</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>7253.05</v>
+      <c r="B8" s="2" t="n">
+        <v>7885.1</v>
       </c>
       <c r="C8" t="n">
-        <v>7177.4</v>
+        <v>7901.65</v>
       </c>
     </row>
     <row r="9">
@@ -535,11 +534,11 @@
           <t>BANBK</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>151.5</v>
+      <c r="B9" s="2" t="n">
+        <v>151.38</v>
       </c>
       <c r="C9" t="n">
-        <v>148.28</v>
+        <v>148.25</v>
       </c>
     </row>
     <row r="10">
@@ -548,11 +547,11 @@
           <t>BHEL</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
-        <v>210.59</v>
+      <c r="B10" s="2" t="n">
+        <v>208.09</v>
       </c>
       <c r="C10" t="n">
-        <v>202.16</v>
+        <v>196.37</v>
       </c>
     </row>
     <row r="11">
@@ -561,11 +560,11 @@
           <t>BARODA</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>229.05</v>
+      <c r="B11" s="2" t="n">
+        <v>213.39</v>
       </c>
       <c r="C11" t="n">
-        <v>222.02</v>
+        <v>222.39</v>
       </c>
     </row>
     <row r="12">
@@ -574,11 +573,11 @@
           <t>BN</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>49443.95</v>
+      <c r="B12" s="2" t="n">
+        <v>49862</v>
       </c>
       <c r="C12" t="n">
-        <v>48892.55</v>
+        <v>49686.5</v>
       </c>
     </row>
     <row r="13">
@@ -587,11 +586,11 @@
           <t>CHAMBAL</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
-        <v>497</v>
+      <c r="B13" s="2" t="n">
+        <v>504.1</v>
       </c>
       <c r="C13" t="n">
-        <v>485.3</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14">
@@ -600,11 +599,11 @@
           <t>COALIND</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>381</v>
+      <c r="B14" s="2" t="n">
+        <v>395.9</v>
       </c>
       <c r="C14" t="n">
-        <v>374.6</v>
+        <v>385.05</v>
       </c>
     </row>
     <row r="15">
@@ -613,11 +612,11 @@
           <t>DIXON</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
-        <v>16944.45</v>
+      <c r="B15" s="2" t="n">
+        <v>14985.95</v>
       </c>
       <c r="C15" t="n">
-        <v>16919.65</v>
+        <v>14659.85</v>
       </c>
     </row>
     <row r="16">
@@ -626,11 +625,11 @@
           <t>DLF</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>742</v>
+      <c r="B16" s="2" t="n">
+        <v>745.05</v>
       </c>
       <c r="C16" t="n">
-        <v>734.8</v>
+        <v>750.05</v>
       </c>
     </row>
     <row r="17">
@@ -639,11 +638,11 @@
           <t>EICHER</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
-        <v>5060.95</v>
+      <c r="B17" s="2" t="n">
+        <v>5194.3</v>
       </c>
       <c r="C17" t="n">
-        <v>5081.9</v>
+        <v>5164.35</v>
       </c>
     </row>
     <row r="18">
@@ -652,11 +651,11 @@
           <t>ESCORTS</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>3564</v>
+      <c r="B18" s="2" t="n">
+        <v>3623.45</v>
       </c>
       <c r="C18" t="n">
-        <v>3478.75</v>
+        <v>3590.95</v>
       </c>
     </row>
     <row r="19">
@@ -665,11 +664,11 @@
           <t>FEDBANK</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n">
-        <v>195.8</v>
+      <c r="B19" s="2" t="n">
+        <v>187.21</v>
       </c>
       <c r="C19" t="n">
-        <v>194.14</v>
+        <v>184.96</v>
       </c>
     </row>
     <row r="20">
@@ -678,11 +677,11 @@
           <t>HCL</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>1792.25</v>
+      <c r="B20" s="2" t="n">
+        <v>1725.45</v>
       </c>
       <c r="C20" t="n">
-        <v>1825.7</v>
+        <v>1713.1</v>
       </c>
     </row>
     <row r="21">
@@ -691,11 +690,11 @@
           <t>HINDALCO</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
-        <v>602.5</v>
+      <c r="B21" s="2" t="n">
+        <v>594.3</v>
       </c>
       <c r="C21" t="n">
-        <v>591.55</v>
+        <v>587.85</v>
       </c>
     </row>
     <row r="22">
@@ -704,11 +703,11 @@
           <t>IGL</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>397.45</v>
+      <c r="B22" s="2" t="n">
+        <v>201.8</v>
       </c>
       <c r="C22" t="n">
-        <v>402.15</v>
+        <v>395.7</v>
       </c>
     </row>
     <row r="23">
@@ -717,11 +716,11 @@
           <t>INDUSIND</t>
         </is>
       </c>
-      <c r="B23" s="3" t="n">
-        <v>975.35</v>
+      <c r="B23" s="2" t="n">
+        <v>991.2</v>
       </c>
       <c r="C23" t="n">
-        <v>962.45</v>
+        <v>957.05</v>
       </c>
     </row>
     <row r="24">
@@ -730,11 +729,11 @@
           <t>JIND</t>
         </is>
       </c>
-      <c r="B24" s="3" t="n">
-        <v>917</v>
+      <c r="B24" s="2" t="n">
+        <v>791.55</v>
       </c>
       <c r="C24" t="n">
-        <v>910.25</v>
+        <v>840.05</v>
       </c>
     </row>
     <row r="25">
@@ -743,11 +742,11 @@
           <t>LIC</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>565.3</v>
+      <c r="B25" s="2" t="n">
+        <v>598.1</v>
       </c>
       <c r="C25" t="n">
-        <v>552.95</v>
+        <v>584.35</v>
       </c>
     </row>
     <row r="26">
@@ -756,11 +755,11 @@
           <t>M&amp;M</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
-        <v>2979.75</v>
+      <c r="B26" s="2" t="n">
+        <v>2989.85</v>
       </c>
       <c r="C26" t="n">
-        <v>2960.25</v>
+        <v>2971.45</v>
       </c>
     </row>
     <row r="27">
@@ -769,11 +768,11 @@
           <t>M&amp;MFIN</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>269.85</v>
+      <c r="B27" s="2" t="n">
+        <v>284.95</v>
       </c>
       <c r="C27" t="n">
-        <v>267.85</v>
+        <v>276.65</v>
       </c>
     </row>
     <row r="28">
@@ -782,11 +781,11 @@
           <t>NIFTY</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
-        <v>23377.55</v>
+      <c r="B28" s="2" t="n">
+        <v>23620.2</v>
       </c>
       <c r="C28" t="n">
-        <v>23265.9</v>
+        <v>23418.3</v>
       </c>
     </row>
     <row r="29">
@@ -795,11 +794,11 @@
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>327</v>
+      <c r="B29" s="2" t="n">
+        <v>324</v>
       </c>
       <c r="C29" t="n">
-        <v>321.35</v>
+        <v>323</v>
       </c>
     </row>
     <row r="30">
@@ -808,11 +807,11 @@
           <t>ONGC</t>
         </is>
       </c>
-      <c r="B30" s="3" t="n">
-        <v>263.35</v>
+      <c r="B30" s="2" t="n">
+        <v>262.61</v>
       </c>
       <c r="C30" t="n">
-        <v>258.18</v>
+        <v>256.72</v>
       </c>
     </row>
     <row r="31">
@@ -821,11 +820,11 @@
           <t>RECLTD</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
-        <v>485.4</v>
+      <c r="B31" s="2" t="n">
+        <v>449.85</v>
       </c>
       <c r="C31" t="n">
-        <v>478.65</v>
+        <v>440.35</v>
       </c>
     </row>
     <row r="32">
@@ -834,11 +833,11 @@
           <t>REL</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>1275</v>
+      <c r="B32" s="2" t="n">
+        <v>1265.1</v>
       </c>
       <c r="C32" t="n">
-        <v>1252.2</v>
+        <v>1253.05</v>
       </c>
     </row>
     <row r="33">
@@ -847,11 +846,11 @@
           <t>SBIN</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
-        <v>767</v>
+      <c r="B33" s="2" t="n">
+        <v>772.9</v>
       </c>
       <c r="C33" t="n">
-        <v>753.7</v>
+        <v>762.6</v>
       </c>
     </row>
     <row r="34">
@@ -860,11 +859,11 @@
           <t>SUNTV</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>652.9</v>
+      <c r="B34" s="2" t="n">
+        <v>618.85</v>
       </c>
       <c r="C34" t="n">
-        <v>653.3</v>
+        <v>631.4</v>
       </c>
     </row>
     <row r="35">
@@ -873,11 +872,11 @@
           <t>TM</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n">
-        <v>775.45</v>
+      <c r="B35" s="2" t="n">
+        <v>716.1</v>
       </c>
       <c r="C35" t="n">
-        <v>763.6</v>
+        <v>696.85</v>
       </c>
     </row>
     <row r="36">
@@ -886,11 +885,11 @@
           <t>TP</t>
         </is>
       </c>
-      <c r="B36" s="3" t="n">
-        <v>369</v>
+      <c r="B36" s="2" t="n">
+        <v>364.5</v>
       </c>
       <c r="C36" t="n">
-        <v>365.45</v>
+        <v>352.15</v>
       </c>
     </row>
     <row r="37">
@@ -899,11 +898,11 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="B37" s="3" t="n">
-        <v>127.81</v>
+      <c r="B37" s="2" t="n">
+        <v>134.62</v>
       </c>
       <c r="C37" t="n">
-        <v>126.53</v>
+        <v>131.12</v>
       </c>
     </row>
     <row r="38">
@@ -913,10 +912,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>450.5</v>
+        <v>441.4</v>
       </c>
       <c r="C38" t="n">
-        <v>435.25</v>
+        <v>432.45</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>444.7</v>
+        <v>392.65</v>
       </c>
       <c r="C2" t="n">
-        <v>438</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5874.65</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5719.35</v>
+        <v>5129.3</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>5160.3</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2287.8</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2252.6</v>
+        <v>2250.6</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2228.3</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>437.3</v>
+        <v>402.1</v>
       </c>
       <c r="C5" t="n">
-        <v>432.8</v>
+        <v>408.8</v>
       </c>
     </row>
     <row r="6">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>216.83</v>
+        <v>199.96</v>
       </c>
       <c r="C6" t="n">
-        <v>210.33</v>
+        <v>206.79</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1736.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1745.2</v>
+        <v>1805.4</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>1840.35</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>7885.1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7901.65</v>
+        <v>8340.450000000001</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>8342.6</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>151.38</v>
+        <v>140.11</v>
       </c>
       <c r="C9" t="n">
-        <v>148.25</v>
+        <v>147.97</v>
       </c>
     </row>
     <row r="10">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>208.09</v>
+        <v>194.12</v>
       </c>
       <c r="C10" t="n">
-        <v>196.37</v>
+        <v>192.11</v>
       </c>
     </row>
     <row r="11">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>213.39</v>
+        <v>202.56</v>
       </c>
       <c r="C11" t="n">
-        <v>222.39</v>
+        <v>204.03</v>
       </c>
     </row>
     <row r="12">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>49862</v>
+        <v>47999.5</v>
       </c>
       <c r="C12" t="n">
-        <v>49686.5</v>
+        <v>48315.35</v>
       </c>
     </row>
     <row r="13">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>504.1</v>
+        <v>563.6</v>
       </c>
       <c r="C13" t="n">
-        <v>494</v>
+        <v>574.05</v>
       </c>
     </row>
     <row r="14">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>395.9</v>
+        <v>379.05</v>
       </c>
       <c r="C14" t="n">
-        <v>385.05</v>
+        <v>375.15</v>
       </c>
     </row>
     <row r="15">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>14985.95</v>
-      </c>
-      <c r="C15" t="n">
-        <v>14659.85</v>
+        <v>13298.9</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>13131.15</v>
       </c>
     </row>
     <row r="16">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>745.05</v>
+        <v>674.1</v>
       </c>
       <c r="C16" t="n">
-        <v>750.05</v>
+        <v>647.1</v>
       </c>
     </row>
     <row r="17">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5194.3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>5164.35</v>
+        <v>4985.55</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>4990.55</v>
       </c>
     </row>
     <row r="18">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3623.45</v>
-      </c>
-      <c r="C18" t="n">
-        <v>3590.95</v>
+        <v>2890.2</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2931.75</v>
       </c>
     </row>
     <row r="19">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>187.21</v>
+        <v>179.12</v>
       </c>
       <c r="C19" t="n">
-        <v>184.96</v>
+        <v>179.12</v>
       </c>
     </row>
     <row r="20">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1725.45</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1713.1</v>
+        <v>1567.85</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>1549.3</v>
       </c>
     </row>
     <row r="21">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>594.3</v>
+        <v>695.5</v>
       </c>
       <c r="C21" t="n">
-        <v>587.85</v>
+        <v>689.15</v>
       </c>
     </row>
     <row r="22">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>201.8</v>
+        <v>187.16</v>
       </c>
       <c r="C22" t="n">
-        <v>395.7</v>
+        <v>183.02</v>
       </c>
     </row>
     <row r="23">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>991.2</v>
+        <v>655.95</v>
       </c>
       <c r="C23" t="n">
-        <v>957.05</v>
+        <v>900.5</v>
       </c>
     </row>
     <row r="24">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>791.55</v>
+        <v>904.85</v>
       </c>
       <c r="C24" t="n">
-        <v>840.05</v>
+        <v>905.3</v>
       </c>
     </row>
     <row r="25">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>598.1</v>
+        <v>533.6</v>
       </c>
       <c r="C25" t="n">
-        <v>584.35</v>
+        <v>528.45</v>
       </c>
     </row>
     <row r="26">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2989.85</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2971.45</v>
+        <v>2645.6</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>2702.6</v>
       </c>
     </row>
     <row r="27">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>284.95</v>
+        <v>268.6</v>
       </c>
       <c r="C27" t="n">
-        <v>276.65</v>
+        <v>272.15</v>
       </c>
     </row>
     <row r="28">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>23620.2</v>
+        <v>22564.3</v>
       </c>
       <c r="C28" t="n">
-        <v>23418.3</v>
+        <v>22515.65</v>
       </c>
     </row>
     <row r="29">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>324</v>
+        <v>330.3</v>
       </c>
       <c r="C29" t="n">
-        <v>323</v>
+        <v>329.4</v>
       </c>
     </row>
     <row r="30">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>262.61</v>
+        <v>226.72</v>
       </c>
       <c r="C30" t="n">
-        <v>256.72</v>
+        <v>223.19</v>
       </c>
     </row>
     <row r="31">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>449.85</v>
+        <v>402.6</v>
       </c>
       <c r="C31" t="n">
-        <v>440.35</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="32">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1265.1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1253.05</v>
+        <v>1247.3</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>1238.4</v>
       </c>
     </row>
     <row r="33">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>772.9</v>
+        <v>729.85</v>
       </c>
       <c r="C33" t="n">
-        <v>762.6</v>
+        <v>728.9</v>
       </c>
     </row>
     <row r="34">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>618.85</v>
+        <v>579.2</v>
       </c>
       <c r="C34" t="n">
-        <v>631.4</v>
+        <v>560.95</v>
       </c>
     </row>
     <row r="35">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>716.1</v>
+        <v>648.05</v>
       </c>
       <c r="C35" t="n">
-        <v>696.85</v>
+        <v>648.15</v>
       </c>
     </row>
     <row r="36">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>364.5</v>
+        <v>352.45</v>
       </c>
       <c r="C36" t="n">
-        <v>352.15</v>
+        <v>352.45</v>
       </c>
     </row>
     <row r="37">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>134.62</v>
+        <v>150.75</v>
       </c>
       <c r="C37" t="n">
-        <v>131.12</v>
+        <v>151.05</v>
       </c>
     </row>
     <row r="38">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>441.4</v>
+        <v>441.55</v>
       </c>
       <c r="C38" t="n">
-        <v>432.45</v>
+        <v>437.4</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,6 +957,9 @@
       <c r="C2" t="n">
         <v>403.85</v>
       </c>
+      <c r="F2" s="2" t="n">
+        <v>381.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -970,6 +973,9 @@
       <c r="C3" t="n">
         <v>6921.25</v>
       </c>
+      <c r="F3" s="2" t="n">
+        <v>5088.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -983,6 +989,9 @@
       <c r="C4" t="n">
         <v>2344.95</v>
       </c>
+      <c r="F4" s="2" t="n">
+        <v>2147.6</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -996,6 +1005,9 @@
       <c r="C5" t="n">
         <v>531.95</v>
       </c>
+      <c r="F5" s="2" t="n">
+        <v>379</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1009,6 +1021,9 @@
       <c r="C6" t="n">
         <v>217.28</v>
       </c>
+      <c r="F6" s="2" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1022,6 +1037,9 @@
       <c r="C7" t="n">
         <v>1569.65</v>
       </c>
+      <c r="F7" s="2" t="n">
+        <v>1789.9</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1035,6 +1053,9 @@
       <c r="C8" t="n">
         <v>6848.25</v>
       </c>
+      <c r="F8" s="2" t="n">
+        <v>8576.35</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1048,6 +1069,9 @@
       <c r="C9" t="n">
         <v>159.05</v>
       </c>
+      <c r="F9" s="2" t="n">
+        <v>147.31</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1061,6 +1085,9 @@
       <c r="C10" t="n">
         <v>235.3</v>
       </c>
+      <c r="F10" s="2" t="n">
+        <v>191.91</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1074,6 +1101,9 @@
       <c r="C11" t="n">
         <v>240.59</v>
       </c>
+      <c r="F11" s="2" t="n">
+        <v>195.7</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1087,6 +1117,9 @@
       <c r="C12" t="n">
         <v>50769.95</v>
       </c>
+      <c r="F12" s="2" t="n">
+        <v>48245</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1100,6 +1133,9 @@
       <c r="C13" t="n">
         <v>509.15</v>
       </c>
+      <c r="F13" s="2" t="n">
+        <v>536.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1113,6 +1149,9 @@
       <c r="C14" t="n">
         <v>17944.9</v>
       </c>
+      <c r="F14" s="2" t="n">
+        <v>363.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1126,6 +1165,9 @@
       <c r="C15" t="n">
         <v>830.7</v>
       </c>
+      <c r="F15" s="2" t="n">
+        <v>14168.15</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1139,6 +1181,9 @@
       <c r="C16" t="n">
         <v>4734.5</v>
       </c>
+      <c r="F16" s="2" t="n">
+        <v>641</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1152,6 +1197,9 @@
       <c r="C17" t="n">
         <v>3162.05</v>
       </c>
+      <c r="F17" s="2" t="n">
+        <v>4808.05</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1165,6 +1213,9 @@
       <c r="C18" t="n">
         <v>194.46</v>
       </c>
+      <c r="F18" s="2" t="n">
+        <v>2958</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1178,6 +1229,9 @@
       <c r="C19" t="n">
         <v>1911.35</v>
       </c>
+      <c r="F19" s="2" t="n">
+        <v>176.3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1191,6 +1245,9 @@
       <c r="C20" t="n">
         <v>622.65</v>
       </c>
+      <c r="F20" s="2" t="n">
+        <v>1536.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1204,6 +1261,9 @@
       <c r="C21" t="n">
         <v>388.3</v>
       </c>
+      <c r="F21" s="2" t="n">
+        <v>640</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1217,6 +1277,9 @@
       <c r="C22" t="n">
         <v>929.45</v>
       </c>
+      <c r="F22" s="2" t="n">
+        <v>180.3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1230,6 +1293,9 @@
       <c r="C23" t="n">
         <v>908.05</v>
       </c>
+      <c r="F23" s="2" t="n">
+        <v>988</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1243,6 +1309,9 @@
       <c r="C24" t="n">
         <v>582.25</v>
       </c>
+      <c r="F24" s="2" t="n">
+        <v>868.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1256,6 +1325,9 @@
       <c r="C25" t="n">
         <v>2906.35</v>
       </c>
+      <c r="F25" s="2" t="n">
+        <v>502.6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1269,6 +1341,9 @@
       <c r="C26" t="n">
         <v>266.05</v>
       </c>
+      <c r="F26" s="2" t="n">
+        <v>2612.85</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1282,6 +1357,9 @@
       <c r="C27" t="n">
         <v>23625.65</v>
       </c>
+      <c r="F27" s="2" t="n">
+        <v>266.55</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1295,6 +1373,9 @@
       <c r="C28" t="n">
         <v>333.25</v>
       </c>
+      <c r="F28" s="2" t="n">
+        <v>22082</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1307,6 +1388,9 @@
       </c>
       <c r="C29" t="n">
         <v>237.1</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>313.55</v>
       </c>
     </row>
     <row r="30">
@@ -1316,6 +1400,9 @@
       <c r="C30" t="n">
         <v>513.25</v>
       </c>
+      <c r="F30" s="2" t="n">
+        <v>226.99</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -1324,6 +1411,9 @@
       <c r="C31" t="n">
         <v>1205.3</v>
       </c>
+      <c r="F31" s="2" t="n">
+        <v>386.65</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -1332,6 +1422,9 @@
       <c r="C32" t="n">
         <v>812</v>
       </c>
+      <c r="F32" s="2" t="n">
+        <v>1160.45</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -1340,6 +1433,9 @@
       <c r="C33" t="n">
         <v>696.85</v>
       </c>
+      <c r="F33" s="2" t="n">
+        <v>716.4</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -1348,6 +1444,9 @@
       <c r="C34" t="n">
         <v>724.05</v>
       </c>
+      <c r="F34" s="2" t="n">
+        <v>569.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -1356,6 +1455,9 @@
       <c r="C35" t="n">
         <v>401.1</v>
       </c>
+      <c r="F35" s="2" t="n">
+        <v>619.5</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -1364,6 +1466,9 @@
       <c r="C36" t="n">
         <v>140.68</v>
       </c>
+      <c r="F36" s="2" t="n">
+        <v>346</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
@@ -1371,6 +1476,14 @@
       </c>
       <c r="C37" t="n">
         <v>2025.35</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>139.29</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="F38" t="n">
+        <v>407.9</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>392.65</v>
+        <v>357.75</v>
       </c>
       <c r="C2" t="n">
-        <v>391</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5129.3</v>
+        <v>5036.2</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>5160.3</v>
+        <v>5064.4</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2250.6</v>
+        <v>2236.9</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>2228.3</v>
+        <v>2285.7</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>402.1</v>
+        <v>407.8</v>
       </c>
       <c r="C5" t="n">
-        <v>408.8</v>
+        <v>401.45</v>
       </c>
     </row>
     <row r="6">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>199.96</v>
+        <v>204.68</v>
       </c>
       <c r="C6" t="n">
-        <v>206.79</v>
+        <v>201.82</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1805.4</v>
+        <v>1895.7</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1840.35</v>
+        <v>1903.2</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8340.450000000001</v>
+        <v>8735.799999999999</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>8342.6</v>
+        <v>8822.25</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>140.11</v>
+        <v>146.86</v>
       </c>
       <c r="C9" t="n">
-        <v>147.97</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>194.12</v>
+        <v>211.81</v>
       </c>
       <c r="C10" t="n">
-        <v>192.11</v>
+        <v>210.94</v>
       </c>
     </row>
     <row r="11">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>202.56</v>
+        <v>230.21</v>
       </c>
       <c r="C11" t="n">
-        <v>204.03</v>
+        <v>235.84</v>
       </c>
     </row>
     <row r="12">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>47999.5</v>
+        <v>50468.6</v>
       </c>
       <c r="C12" t="n">
-        <v>48315.35</v>
+        <v>50768.2</v>
       </c>
     </row>
     <row r="13">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>563.6</v>
+        <v>638.05</v>
       </c>
       <c r="C13" t="n">
-        <v>574.05</v>
+        <v>631.65</v>
       </c>
     </row>
     <row r="14">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>379.05</v>
+        <v>374.6</v>
       </c>
       <c r="C14" t="n">
-        <v>375.15</v>
+        <v>382.85</v>
       </c>
     </row>
     <row r="15">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>13298.9</v>
+        <v>13282.45</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>13131.15</v>
+        <v>12991.8</v>
       </c>
     </row>
     <row r="16">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>674.1</v>
+        <v>612.85</v>
       </c>
       <c r="C16" t="n">
-        <v>647.1</v>
+        <v>621.55</v>
       </c>
     </row>
     <row r="17">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4985.55</v>
+        <v>5258.3</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>4990.55</v>
+        <v>5231.35</v>
       </c>
     </row>
     <row r="18">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2890.2</v>
+        <v>3128.75</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>2931.75</v>
+        <v>3075.35</v>
       </c>
     </row>
     <row r="19">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>179.12</v>
+        <v>189.96</v>
       </c>
       <c r="C19" t="n">
-        <v>179.12</v>
+        <v>190.53</v>
       </c>
     </row>
     <row r="20">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1567.85</v>
+        <v>1380</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1549.3</v>
+        <v>1403.35</v>
       </c>
     </row>
     <row r="21">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>695.5</v>
+        <v>564</v>
       </c>
       <c r="C21" t="n">
-        <v>689.15</v>
+        <v>568.35</v>
       </c>
     </row>
     <row r="22">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>187.16</v>
+        <v>174.88</v>
       </c>
       <c r="C22" t="n">
-        <v>183.02</v>
+        <v>180.16</v>
       </c>
     </row>
     <row r="23">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>655.95</v>
+        <v>678.55</v>
       </c>
       <c r="C23" t="n">
-        <v>900.5</v>
+        <v>679.65</v>
       </c>
     </row>
     <row r="24">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>904.85</v>
+        <v>786.9</v>
       </c>
       <c r="C24" t="n">
-        <v>905.3</v>
+        <v>801.85</v>
       </c>
     </row>
     <row r="25">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>533.6</v>
+        <v>556.35</v>
       </c>
       <c r="C25" t="n">
-        <v>528.45</v>
+        <v>565.85</v>
       </c>
     </row>
     <row r="26">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2645.6</v>
+        <v>2523.1</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2702.6</v>
+        <v>2523.65</v>
       </c>
     </row>
     <row r="27">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>268.6</v>
+        <v>257.6</v>
       </c>
       <c r="C27" t="n">
-        <v>272.15</v>
+        <v>258.8</v>
       </c>
     </row>
     <row r="28">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>22564.3</v>
+        <v>22479.65</v>
       </c>
       <c r="C28" t="n">
-        <v>22515.65</v>
+        <v>22630.35</v>
       </c>
     </row>
     <row r="29">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>330.3</v>
+        <v>349.35</v>
       </c>
       <c r="C29" t="n">
-        <v>329.4</v>
+        <v>352.95</v>
       </c>
     </row>
     <row r="30">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>226.72</v>
+        <v>221.94</v>
       </c>
       <c r="C30" t="n">
-        <v>223.19</v>
+        <v>226.66</v>
       </c>
     </row>
     <row r="31">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>402.6</v>
+        <v>389.45</v>
       </c>
       <c r="C31" t="n">
-        <v>394.2</v>
+        <v>395.85</v>
       </c>
     </row>
     <row r="32">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1247.3</v>
+        <v>1185.35</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>1238.4</v>
+        <v>1182.2</v>
       </c>
     </row>
     <row r="33">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>729.85</v>
+        <v>742.2</v>
       </c>
       <c r="C33" t="n">
-        <v>728.9</v>
+        <v>768.6</v>
       </c>
     </row>
     <row r="34">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>579.2</v>
+        <v>647.95</v>
       </c>
       <c r="C34" t="n">
-        <v>560.95</v>
+        <v>652.8</v>
       </c>
     </row>
     <row r="35">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>648.05</v>
+        <v>582.9</v>
       </c>
       <c r="C35" t="n">
-        <v>648.15</v>
+        <v>588.85</v>
       </c>
     </row>
     <row r="36">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>352.45</v>
+        <v>358.25</v>
       </c>
       <c r="C36" t="n">
-        <v>352.45</v>
+        <v>359.7</v>
       </c>
     </row>
     <row r="37">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>150.75</v>
+        <v>127.18</v>
       </c>
       <c r="C37" t="n">
-        <v>151.05</v>
+        <v>130.28</v>
       </c>
     </row>
     <row r="38">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>441.55</v>
+        <v>370.55</v>
       </c>
       <c r="C38" t="n">
-        <v>437.4</v>
+        <v>376.1</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="ltp" sheetId="1" state="visible" r:id="rId1"/>
@@ -420,9 +420,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>357.75</v>
+        <v>474.65</v>
       </c>
       <c r="C2" t="n">
-        <v>364</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5036.2</v>
+        <v>5820</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>5064.4</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2236.9</v>
+        <v>2555</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>2285.7</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>407.8</v>
+        <v>494.25</v>
       </c>
       <c r="C5" t="n">
-        <v>401.45</v>
+        <v>480.45</v>
       </c>
     </row>
     <row r="6">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>204.68</v>
+        <v>237.33</v>
       </c>
       <c r="C6" t="n">
-        <v>201.82</v>
+        <v>239.36</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1895.7</v>
+        <v>2033.6</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>1903.2</v>
+        <v>2041.9</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>8735.799999999999</v>
+        <v>9167</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>8822.25</v>
+        <v>9188.5</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>146.86</v>
+        <v>170.09</v>
       </c>
       <c r="C9" t="n">
-        <v>150</v>
+        <v>168.99</v>
       </c>
     </row>
     <row r="10">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>211.81</v>
+        <v>250.35</v>
       </c>
       <c r="C10" t="n">
-        <v>210.94</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="11">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>230.21</v>
+        <v>236.92</v>
       </c>
       <c r="C11" t="n">
-        <v>235.84</v>
+        <v>234.38</v>
       </c>
     </row>
     <row r="12">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>50468.6</v>
+        <v>55503.2</v>
       </c>
       <c r="C12" t="n">
-        <v>50768.2</v>
+        <v>55399.6</v>
       </c>
     </row>
     <row r="13">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>638.05</v>
+        <v>632.1</v>
       </c>
       <c r="C13" t="n">
-        <v>631.65</v>
+        <v>636.1</v>
       </c>
     </row>
     <row r="14">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>374.6</v>
+        <v>404.8</v>
       </c>
       <c r="C14" t="n">
-        <v>382.85</v>
+        <v>404.65</v>
       </c>
     </row>
     <row r="15">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>13282.45</v>
+        <v>16660</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>12991.8</v>
+        <v>16433</v>
       </c>
     </row>
     <row r="16">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>612.85</v>
+        <v>715.9</v>
       </c>
       <c r="C16" t="n">
-        <v>621.55</v>
+        <v>709.05</v>
       </c>
     </row>
     <row r="17">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5258.3</v>
+        <v>5509.5</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>5231.35</v>
+        <v>5466</v>
       </c>
     </row>
     <row r="18">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3128.75</v>
+        <v>3551.5</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>3075.35</v>
+        <v>3543.4</v>
       </c>
     </row>
     <row r="19">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>189.96</v>
+        <v>199.03</v>
       </c>
       <c r="C19" t="n">
-        <v>190.53</v>
+        <v>198.84</v>
       </c>
     </row>
     <row r="20">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1380</v>
+        <v>1659.9</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1403.35</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="21">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>564</v>
+        <v>657.55</v>
       </c>
       <c r="C21" t="n">
-        <v>568.35</v>
+        <v>661.35</v>
       </c>
     </row>
     <row r="22">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>174.88</v>
+        <v>209.2</v>
       </c>
       <c r="C22" t="n">
-        <v>180.16</v>
+        <v>204.87</v>
       </c>
     </row>
     <row r="23">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>678.55</v>
+        <v>780.2</v>
       </c>
       <c r="C23" t="n">
-        <v>679.65</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="24">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>786.9</v>
+        <v>981.6</v>
       </c>
       <c r="C24" t="n">
-        <v>801.85</v>
+        <v>968.3</v>
       </c>
     </row>
     <row r="25">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>556.35</v>
+        <v>621.1</v>
       </c>
       <c r="C25" t="n">
-        <v>565.85</v>
+        <v>624.95</v>
       </c>
     </row>
     <row r="26">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>2523.1</v>
+        <v>3135.6</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>2523.65</v>
+        <v>3144.3</v>
       </c>
     </row>
     <row r="27">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>257.6</v>
+        <v>266.95</v>
       </c>
       <c r="C27" t="n">
-        <v>258.8</v>
+        <v>265.35</v>
       </c>
     </row>
     <row r="28">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>22479.65</v>
+        <v>25078.7</v>
       </c>
       <c r="C28" t="n">
-        <v>22630.35</v>
+        <v>25078.7</v>
       </c>
     </row>
     <row r="29">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>349.35</v>
+        <v>343.1</v>
       </c>
       <c r="C29" t="n">
-        <v>352.95</v>
+        <v>341.95</v>
       </c>
     </row>
     <row r="30">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>221.94</v>
+        <v>247.27</v>
       </c>
       <c r="C30" t="n">
-        <v>226.66</v>
+        <v>247.61</v>
       </c>
     </row>
     <row r="31">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>389.45</v>
+        <v>406.45</v>
       </c>
       <c r="C31" t="n">
-        <v>395.85</v>
+        <v>394.35</v>
       </c>
     </row>
     <row r="32">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1185.35</v>
+        <v>1456.4</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>1182.2</v>
+        <v>1454.2</v>
       </c>
     </row>
     <row r="33">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>742.2</v>
+        <v>792.1</v>
       </c>
       <c r="C33" t="n">
-        <v>768.6</v>
+        <v>807.75</v>
       </c>
     </row>
     <row r="34">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>647.95</v>
+        <v>629.2</v>
       </c>
       <c r="C34" t="n">
-        <v>652.8</v>
+        <v>630.3</v>
       </c>
     </row>
     <row r="35">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>582.9</v>
+        <v>730.7</v>
       </c>
       <c r="C35" t="n">
-        <v>588.85</v>
+        <v>728.1</v>
       </c>
     </row>
     <row r="36">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>358.25</v>
+        <v>405.8</v>
       </c>
       <c r="C36" t="n">
-        <v>359.7</v>
+        <v>397.95</v>
       </c>
     </row>
     <row r="37">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>127.18</v>
+        <v>157.55</v>
       </c>
       <c r="C37" t="n">
-        <v>130.28</v>
+        <v>157.35</v>
       </c>
     </row>
     <row r="38">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>370.55</v>
+        <v>441.2</v>
       </c>
       <c r="C38" t="n">
-        <v>376.1</v>
+        <v>443.8</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +931,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -444,10 +444,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>474.65</v>
+        <v>469.3</v>
       </c>
       <c r="C2" t="n">
-        <v>464</v>
+        <v>468.85</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5820</v>
+        <v>5961</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>5735</v>
+        <v>5924</v>
       </c>
     </row>
     <row r="4">
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>2520</v>
+        <v>2487.6</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>494.25</v>
+        <v>494.7</v>
       </c>
       <c r="C5" t="n">
-        <v>480.45</v>
+        <v>491.85</v>
       </c>
     </row>
     <row r="6">
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>237.33</v>
+        <v>239.61</v>
       </c>
       <c r="C6" t="n">
-        <v>239.36</v>
+        <v>238.8</v>
       </c>
     </row>
     <row r="7">
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2033.6</v>
+        <v>2036.5</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>2041.9</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="8">
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>9167</v>
+        <v>9243.5</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>9188.5</v>
+        <v>9139</v>
       </c>
     </row>
     <row r="9">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>170.09</v>
+        <v>165.46</v>
       </c>
       <c r="C9" t="n">
-        <v>168.99</v>
+        <v>165.6</v>
       </c>
     </row>
     <row r="10">
@@ -548,10 +548,10 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>250.35</v>
+        <v>254.8</v>
       </c>
       <c r="C10" t="n">
-        <v>245.68</v>
+        <v>247.57</v>
       </c>
     </row>
     <row r="11">
@@ -561,10 +561,10 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>236.92</v>
+        <v>243.04</v>
       </c>
       <c r="C11" t="n">
-        <v>234.38</v>
+        <v>241.23</v>
       </c>
     </row>
     <row r="12">
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>55503.2</v>
+        <v>55495.6</v>
       </c>
       <c r="C12" t="n">
-        <v>55399.6</v>
+        <v>55068.4</v>
       </c>
     </row>
     <row r="13">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>632.1</v>
+        <v>594.3</v>
       </c>
       <c r="C13" t="n">
-        <v>636.1</v>
+        <v>591.1</v>
       </c>
     </row>
     <row r="14">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>404.8</v>
+        <v>401.5</v>
       </c>
       <c r="C14" t="n">
-        <v>404.65</v>
+        <v>398.85</v>
       </c>
     </row>
     <row r="15">
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>16660</v>
+        <v>15019</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>16433</v>
+        <v>15170</v>
       </c>
     </row>
     <row r="16">
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>715.9</v>
+        <v>776.5</v>
       </c>
       <c r="C16" t="n">
-        <v>709.05</v>
+        <v>775.8</v>
       </c>
     </row>
     <row r="17">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5509.5</v>
+        <v>5400</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>5466</v>
+        <v>5387</v>
       </c>
     </row>
     <row r="18">
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3551.5</v>
+        <v>3510.6</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>3543.4</v>
+        <v>3504.7</v>
       </c>
     </row>
     <row r="19">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>199.03</v>
+        <v>203.43</v>
       </c>
       <c r="C19" t="n">
-        <v>198.84</v>
+        <v>201.17</v>
       </c>
     </row>
     <row r="20">
@@ -678,10 +678,10 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1659.9</v>
+        <v>1648.2</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1696</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="21">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>657.55</v>
+        <v>650.1</v>
       </c>
       <c r="C21" t="n">
-        <v>661.35</v>
+        <v>649.55</v>
       </c>
     </row>
     <row r="22">
@@ -704,10 +704,10 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>209.2</v>
+        <v>205.83</v>
       </c>
       <c r="C22" t="n">
-        <v>204.87</v>
+        <v>204.27</v>
       </c>
     </row>
     <row r="23">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>780.2</v>
+        <v>793.4</v>
       </c>
       <c r="C23" t="n">
-        <v>780.5</v>
+        <v>785</v>
       </c>
     </row>
     <row r="24">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>981.6</v>
+        <v>953.4</v>
       </c>
       <c r="C24" t="n">
-        <v>968.3</v>
+        <v>959.95</v>
       </c>
     </row>
     <row r="25">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>621.1</v>
+        <v>596.95</v>
       </c>
       <c r="C25" t="n">
-        <v>624.95</v>
+        <v>593.3</v>
       </c>
     </row>
     <row r="26">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>3135.6</v>
+        <v>3012.7</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>3144.3</v>
+        <v>3006.3</v>
       </c>
     </row>
     <row r="27">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>266.95</v>
+        <v>256.1</v>
       </c>
       <c r="C27" t="n">
-        <v>265.35</v>
+        <v>256.1</v>
       </c>
     </row>
     <row r="28">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>25078.7</v>
+        <v>24879.9</v>
       </c>
       <c r="C28" t="n">
-        <v>25078.7</v>
+        <v>24652.2</v>
       </c>
     </row>
     <row r="29">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>343.1</v>
+        <v>344.6</v>
       </c>
       <c r="C29" t="n">
-        <v>341.95</v>
+        <v>341.4</v>
       </c>
     </row>
     <row r="30">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>247.27</v>
+        <v>244.24</v>
       </c>
       <c r="C30" t="n">
-        <v>247.61</v>
+        <v>241.67</v>
       </c>
     </row>
     <row r="31">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>406.45</v>
+        <v>402.5</v>
       </c>
       <c r="C31" t="n">
-        <v>394.35</v>
+        <v>401.8</v>
       </c>
     </row>
     <row r="32">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1456.4</v>
+        <v>1426.8</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>1454.2</v>
+        <v>1409.4</v>
       </c>
     </row>
     <row r="33">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>792.1</v>
+        <v>790.5</v>
       </c>
       <c r="C33" t="n">
-        <v>807.75</v>
+        <v>785.25</v>
       </c>
     </row>
     <row r="34">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>629.2</v>
+        <v>633.4</v>
       </c>
       <c r="C34" t="n">
-        <v>630.3</v>
+        <v>635.4</v>
       </c>
     </row>
     <row r="35">
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>730.7</v>
+        <v>718.25</v>
       </c>
       <c r="C35" t="n">
-        <v>728.1</v>
+        <v>717.45</v>
       </c>
     </row>
     <row r="36">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>405.8</v>
+        <v>402.05</v>
       </c>
       <c r="C36" t="n">
-        <v>397.95</v>
+        <v>395.6</v>
       </c>
     </row>
     <row r="37">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>157.55</v>
+        <v>162.97</v>
       </c>
       <c r="C37" t="n">
-        <v>157.35</v>
+        <v>161.29</v>
       </c>
     </row>
     <row r="38">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>441.2</v>
+        <v>440.05</v>
       </c>
       <c r="C38" t="n">
-        <v>443.8</v>
+        <v>435.1</v>
       </c>
     </row>
   </sheetData>

--- a/ltp prev.xlsx
+++ b/ltp prev.xlsx
@@ -10,7 +10,7 @@
     <sheet name="30" sheetId="1" r:id="rId1"/>
     <sheet name="15" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -940,7 +940,9 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>5188.3999999999996</v>
+      </c>
       <c r="C2" s="1"/>
       <c r="F2" s="2"/>
     </row>
@@ -948,7 +950,9 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2">
+        <v>2288.6999999999998</v>
+      </c>
       <c r="C3" s="1"/>
       <c r="F3" s="2"/>
     </row>
@@ -956,14 +960,18 @@
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>7736</v>
+      </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2">
+        <v>1966.1</v>
+      </c>
       <c r="C5" s="1"/>
       <c r="F5" s="2"/>
     </row>
@@ -971,7 +979,9 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>896.3</v>
+      </c>
       <c r="C6" s="1"/>
       <c r="F6" s="2"/>
     </row>
@@ -979,35 +989,45 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>216.97</v>
+      </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>377.05</v>
+      </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>569.75</v>
+      </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2">
+        <v>1731.8</v>
+      </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2">
+        <v>17759</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="F11" s="2"/>
     </row>
@@ -1015,14 +1035,18 @@
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2">
+        <v>764.4</v>
+      </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2">
+        <v>2004.4</v>
+      </c>
       <c r="C13" s="1"/>
       <c r="F13" s="2"/>
     </row>
@@ -1030,7 +1054,9 @@
       <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>4451</v>
+      </c>
       <c r="C14" s="1"/>
       <c r="F14" s="2"/>
     </row>
@@ -1038,14 +1064,18 @@
       <c r="A15" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>874.7</v>
+      </c>
       <c r="F15" s="2"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2">
+        <v>7707.5</v>
+      </c>
       <c r="C16" s="1"/>
       <c r="F16" s="2"/>
     </row>
@@ -1053,14 +1083,18 @@
       <c r="A17" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2">
+        <v>24813.1</v>
+      </c>
       <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2">
+        <v>1372.6</v>
+      </c>
       <c r="C18" s="1"/>
       <c r="F18" s="2"/>
     </row>
@@ -1068,7 +1102,9 @@
       <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2">
+        <v>692.05</v>
+      </c>
       <c r="F19" s="2"/>
     </row>
   </sheetData>
